--- a/exports/trend_1d/INDIANB_full_report.xlsx
+++ b/exports/trend_1d/INDIANB_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q76"/>
+  <dimension ref="A1:U76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>11.3</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42033</v>
+        <v>42034</v>
       </c>
       <c r="H2" t="n">
-        <v>189.85</v>
+        <v>177.3</v>
       </c>
       <c r="I2" t="n">
         <v>182.314</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K2" t="n">
-        <v>-7.64</v>
+        <v>-13.74</v>
       </c>
       <c r="L2" t="n">
-        <v>9.32</v>
+        <v>16.64</v>
       </c>
       <c r="M2" t="n">
         <v>0.4</v>
       </c>
       <c r="N2" t="n">
-        <v>5.24</v>
+        <v>6.61</v>
       </c>
       <c r="O2" t="n">
         <v>0.49</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>17.88</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42137</v>
+        <v>42138</v>
       </c>
       <c r="H3" t="n">
-        <v>148</v>
+        <v>151.9</v>
       </c>
       <c r="I3" t="n">
         <v>151.6635043162976</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K3" t="n">
-        <v>16.53</v>
+        <v>14.33</v>
       </c>
       <c r="L3" t="n">
         <v>8.630000000000001</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>12.05</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42160</v>
+        <v>42163</v>
       </c>
       <c r="H4" t="n">
-        <v>144.65</v>
+        <v>139.05</v>
       </c>
       <c r="I4" t="n">
         <v>143.7300996265506</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K4" t="n">
-        <v>-4.77</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>5.07</v>
+        <v>8.85</v>
       </c>
       <c r="M4" t="n">
         <v>1.94</v>
       </c>
       <c r="N4" t="n">
-        <v>3.41</v>
+        <v>3.87</v>
       </c>
       <c r="O4" t="n">
         <v>2.64</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,25 +764,25 @@
         <v>14.09</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42219</v>
+        <v>42220</v>
       </c>
       <c r="H5" t="n">
-        <v>138.25</v>
+        <v>146.7</v>
       </c>
       <c r="I5" t="n">
         <v>138.3923485058844</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K5" t="n">
-        <v>0.58</v>
+        <v>-5.5</v>
       </c>
       <c r="L5" t="n">
-        <v>6.29</v>
+        <v>6.44</v>
       </c>
       <c r="M5" t="n">
-        <v>1.98</v>
+        <v>2.75</v>
       </c>
       <c r="N5" t="n">
         <v>9.380000000000001</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>17.08</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42237</v>
+        <v>42240</v>
       </c>
       <c r="H6" t="n">
-        <v>133.4</v>
+        <v>119.1</v>
       </c>
       <c r="I6" t="n">
         <v>129.2958997131527</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K6" t="n">
-        <v>-9.07</v>
+        <v>-18.81</v>
       </c>
       <c r="L6" t="n">
-        <v>11.49</v>
+        <v>21.85</v>
       </c>
       <c r="M6" t="n">
-        <v>1.03</v>
+        <v>2.32</v>
       </c>
       <c r="N6" t="n">
-        <v>5.77</v>
+        <v>10.72</v>
       </c>
       <c r="O6" t="n">
         <v>6.11</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>27.05</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42431</v>
+        <v>42432</v>
       </c>
       <c r="H7" t="n">
-        <v>80.45</v>
+        <v>87.95</v>
       </c>
       <c r="I7" t="n">
         <v>83.93325936076219</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K7" t="n">
-        <v>32.45</v>
+        <v>26.15</v>
       </c>
       <c r="L7" t="n">
         <v>15.66</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>130</v>
+        <v>131</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>8</v>
+      </c>
+      <c r="U7" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>20.19</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42494</v>
+        <v>42495</v>
       </c>
       <c r="H8" t="n">
-        <v>91</v>
+        <v>87.5</v>
       </c>
       <c r="I8" t="n">
         <v>88.72731240641922</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K8" t="n">
-        <v>3.47</v>
+        <v>-0.51</v>
       </c>
       <c r="L8" t="n">
         <v>9.210000000000001</v>
@@ -897,7 +992,7 @@
         <v>2.04</v>
       </c>
       <c r="N8" t="n">
-        <v>3.06</v>
+        <v>3.85</v>
       </c>
       <c r="O8" t="n">
         <v>9.32</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>11.62</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42527</v>
+        <v>42528</v>
       </c>
       <c r="H9" t="n">
-        <v>90.84999999999999</v>
+        <v>92.95</v>
       </c>
       <c r="I9" t="n">
         <v>92.56528776676988</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.83</v>
+        <v>-6.23</v>
       </c>
       <c r="L9" t="n">
-        <v>4.97</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M9" t="n">
         <v>1.29</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>9.24</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42724</v>
+        <v>42725</v>
       </c>
       <c r="H10" t="n">
-        <v>209.65</v>
+        <v>202.4</v>
       </c>
       <c r="I10" t="n">
         <v>202.6420781372569</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K10" t="n">
-        <v>125.55</v>
+        <v>117.75</v>
       </c>
       <c r="L10" t="n">
         <v>2.37</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>133</v>
+        <v>134</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U10" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>17.41</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42745</v>
+        <v>42746</v>
       </c>
       <c r="H11" t="n">
-        <v>224.75</v>
+        <v>237.7</v>
       </c>
       <c r="I11" t="n">
         <v>226.6602302569038</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K11" t="n">
-        <v>-11.04</v>
+        <v>-17.44</v>
       </c>
       <c r="L11" t="n">
-        <v>15.39</v>
+        <v>18.82</v>
       </c>
       <c r="M11" t="n">
         <v>1.62</v>
       </c>
       <c r="N11" t="n">
-        <v>4.28</v>
+        <v>5.76</v>
       </c>
       <c r="O11" t="n">
         <v>-3.46</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>13.44</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42803</v>
+        <v>42804</v>
       </c>
       <c r="H12" t="n">
-        <v>258.75</v>
+        <v>255</v>
       </c>
       <c r="I12" t="n">
         <v>258.1353557513056</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K12" t="n">
-        <v>8.859999999999999</v>
+        <v>7.28</v>
       </c>
       <c r="L12" t="n">
         <v>5.13</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>12.59</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42846</v>
+        <v>42849</v>
       </c>
       <c r="H13" t="n">
-        <v>248.3</v>
+        <v>272.2</v>
       </c>
       <c r="I13" t="n">
         <v>271.4699895664916</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K13" t="n">
-        <v>2.63</v>
+        <v>-6.75</v>
       </c>
       <c r="L13" t="n">
-        <v>7.25</v>
+        <v>8.08</v>
       </c>
       <c r="M13" t="n">
         <v>2.41</v>
       </c>
       <c r="N13" t="n">
-        <v>5.31</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="O13" t="n">
         <v>-1.45</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>14.94</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42881</v>
+        <v>42884</v>
       </c>
       <c r="H14" t="n">
-        <v>311.25</v>
+        <v>302.25</v>
       </c>
       <c r="I14" t="n">
         <v>306.2873264018033</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K14" t="n">
-        <v>14.35</v>
+        <v>11.04</v>
       </c>
       <c r="L14" t="n">
         <v>8.449999999999999</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>15.67</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42929</v>
+        <v>42930</v>
       </c>
       <c r="H15" t="n">
-        <v>290.75</v>
+        <v>301.85</v>
       </c>
       <c r="I15" t="n">
         <v>296.3501032217482</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K15" t="n">
-        <v>3.8</v>
+        <v>0.13</v>
       </c>
       <c r="L15" t="n">
         <v>4.52</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>14.33</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42956</v>
+        <v>42957</v>
       </c>
       <c r="H16" t="n">
-        <v>282.8</v>
+        <v>261.45</v>
       </c>
       <c r="I16" t="n">
         <v>281.0878646541098</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K16" t="n">
-        <v>-6.31</v>
+        <v>-13.38</v>
       </c>
       <c r="L16" t="n">
-        <v>7.01</v>
+        <v>15.24</v>
       </c>
       <c r="M16" t="n">
         <v>0.66</v>
       </c>
       <c r="N16" t="n">
-        <v>4.15</v>
+        <v>7.55</v>
       </c>
       <c r="O16" t="n">
         <v>3.82</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>16.15</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43032</v>
+        <v>43033</v>
       </c>
       <c r="H17" t="n">
-        <v>258</v>
+        <v>312.4</v>
       </c>
       <c r="I17" t="n">
         <v>271.9852060827945</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K17" t="n">
-        <v>1.32</v>
+        <v>-19.49</v>
       </c>
       <c r="L17" t="n">
-        <v>12.83</v>
+        <v>21.9</v>
       </c>
       <c r="M17" t="n">
-        <v>2.17</v>
+        <v>6.57</v>
       </c>
       <c r="N17" t="n">
-        <v>5.02</v>
+        <v>21.09</v>
       </c>
       <c r="O17" t="n">
         <v>-7.55</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>17.74</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43131</v>
+        <v>43132</v>
       </c>
       <c r="H18" t="n">
-        <v>346.2</v>
+        <v>337.6</v>
       </c>
       <c r="I18" t="n">
         <v>346.1419927300481</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K18" t="n">
-        <v>10.82</v>
+        <v>8.07</v>
       </c>
       <c r="L18" t="n">
         <v>11.99</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>13.75</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43199</v>
+        <v>43200</v>
       </c>
       <c r="H19" t="n">
-        <v>307.4</v>
+        <v>309.35</v>
       </c>
       <c r="I19" t="n">
         <v>309.276704334639</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K19" t="n">
-        <v>8.949999999999999</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="L19" t="n">
         <v>4.01</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>11.47</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43294</v>
+        <v>43297</v>
       </c>
       <c r="H20" t="n">
-        <v>319.6</v>
+        <v>308.25</v>
       </c>
       <c r="I20" t="n">
         <v>312.0970826329923</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K20" t="n">
-        <v>3.31</v>
+        <v>-0.36</v>
       </c>
       <c r="L20" t="n">
         <v>9.49</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>12.63</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43308</v>
+        <v>43311</v>
       </c>
       <c r="H21" t="n">
-        <v>337.35</v>
+        <v>345.9</v>
       </c>
       <c r="I21" t="n">
         <v>341.4614123465261</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K21" t="n">
-        <v>-9.44</v>
+        <v>-12.21</v>
       </c>
       <c r="L21" t="n">
-        <v>10.4</v>
+        <v>14.6</v>
       </c>
       <c r="M21" t="n">
         <v>0.9</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>11.89</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43333</v>
+        <v>43335</v>
       </c>
       <c r="H22" t="n">
-        <v>325.8</v>
+        <v>318.95</v>
       </c>
       <c r="I22" t="n">
         <v>319.9311780999376</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K22" t="n">
-        <v>-5.81</v>
+        <v>-7.79</v>
       </c>
       <c r="L22" t="n">
         <v>8.300000000000001</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>11.89</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43402</v>
+        <v>43403</v>
       </c>
       <c r="H23" t="n">
-        <v>230.5</v>
+        <v>245.05</v>
       </c>
       <c r="I23" t="n">
         <v>244.8813594662519</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K23" t="n">
-        <v>27.73</v>
+        <v>23.17</v>
       </c>
       <c r="L23" t="n">
         <v>2.52</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>20.74</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43439</v>
+        <v>43440</v>
       </c>
       <c r="H24" t="n">
-        <v>212.15</v>
+        <v>206.35</v>
       </c>
       <c r="I24" t="n">
         <v>208.2344705741499</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K24" t="n">
-        <v>-13.43</v>
+        <v>-15.79</v>
       </c>
       <c r="L24" t="n">
-        <v>14.57</v>
+        <v>16.81</v>
       </c>
       <c r="M24" t="n">
         <v>1.82</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>13.21</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43451</v>
+        <v>43452</v>
       </c>
       <c r="H25" t="n">
-        <v>226.5</v>
+        <v>232.3</v>
       </c>
       <c r="I25" t="n">
         <v>232.0719408422893</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K25" t="n">
-        <v>-9.76</v>
+        <v>-12.58</v>
       </c>
       <c r="L25" t="n">
-        <v>12.26</v>
+        <v>12.89</v>
       </c>
       <c r="M25" t="n">
         <v>0.53</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>13.08</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43490</v>
+        <v>43493</v>
       </c>
       <c r="H26" t="n">
-        <v>227.6</v>
+        <v>208.5</v>
       </c>
       <c r="I26" t="n">
         <v>225.9104763644862</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.02</v>
+        <v>-10.25</v>
       </c>
       <c r="L26" t="n">
-        <v>5.06</v>
+        <v>12.59</v>
       </c>
       <c r="M26" t="n">
         <v>0.91</v>
       </c>
       <c r="N26" t="n">
-        <v>6.85</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="O26" t="n">
         <v>2.56</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>18.94</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43509</v>
+        <v>43510</v>
       </c>
       <c r="H27" t="n">
-        <v>210.05</v>
+        <v>220.8</v>
       </c>
       <c r="I27" t="n">
         <v>220.6135809608314</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.74</v>
+        <v>-5.9</v>
       </c>
       <c r="L27" t="n">
-        <v>8.44</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="M27" t="n">
         <v>1.37</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>17.03</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43577</v>
+        <v>43578</v>
       </c>
       <c r="H28" t="n">
-        <v>244.75</v>
+        <v>241.4</v>
       </c>
       <c r="I28" t="n">
         <v>241.6162823097431</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K28" t="n">
-        <v>10.85</v>
+        <v>9.33</v>
       </c>
       <c r="L28" t="n">
         <v>10.3</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>12.69</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43608</v>
+        <v>43609</v>
       </c>
       <c r="H29" t="n">
-        <v>241.85</v>
+        <v>253.4</v>
       </c>
       <c r="I29" t="n">
         <v>247.7106092601696</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.19</v>
+        <v>-4.97</v>
       </c>
       <c r="L29" t="n">
         <v>6.34</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>15.18</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43651</v>
+        <v>43654</v>
       </c>
       <c r="H30" t="n">
-        <v>245.2</v>
+        <v>230.55</v>
       </c>
       <c r="I30" t="n">
         <v>235.3550785424859</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K30" t="n">
-        <v>-3.24</v>
+        <v>-9.02</v>
       </c>
       <c r="L30" t="n">
-        <v>5.98</v>
+        <v>10.04</v>
       </c>
       <c r="M30" t="n">
         <v>1.27</v>
       </c>
       <c r="N30" t="n">
-        <v>5.01</v>
+        <v>5.97</v>
       </c>
       <c r="O30" t="n">
         <v>4.78</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>14.82</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43704</v>
+        <v>43705</v>
       </c>
       <c r="H31" t="n">
-        <v>183.9</v>
+        <v>187.4</v>
       </c>
       <c r="I31" t="n">
         <v>187.0080857447115</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K31" t="n">
-        <v>20.23</v>
+        <v>18.72</v>
       </c>
       <c r="L31" t="n">
         <v>6.27</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>18.7</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43724</v>
+        <v>43725</v>
       </c>
       <c r="H32" t="n">
-        <v>156.55</v>
+        <v>152.2</v>
       </c>
       <c r="I32" t="n">
         <v>153.4791624428948</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K32" t="n">
-        <v>-16.46</v>
+        <v>-18.78</v>
       </c>
       <c r="L32" t="n">
-        <v>17.29</v>
+        <v>19.32</v>
       </c>
       <c r="M32" t="n">
         <v>4.45</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>17.87</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43760</v>
+        <v>43761</v>
       </c>
       <c r="H33" t="n">
-        <v>120.6</v>
+        <v>136.45</v>
       </c>
       <c r="I33" t="n">
         <v>122.2078775555765</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K33" t="n">
-        <v>20.76</v>
+        <v>10.35</v>
       </c>
       <c r="L33" t="n">
         <v>3.81</v>
@@ -2322,7 +2717,7 @@
         <v>2.06</v>
       </c>
       <c r="N33" t="n">
-        <v>7.78</v>
+        <v>13.14</v>
       </c>
       <c r="O33" t="n">
         <v>-2.78</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>21.21</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43815</v>
+        <v>43816</v>
       </c>
       <c r="H34" t="n">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="I34" t="n">
         <v>108.7073406315991</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K34" t="n">
-        <v>-18.65</v>
+        <v>-23.05</v>
       </c>
       <c r="L34" t="n">
-        <v>21.25</v>
+        <v>23.71</v>
       </c>
       <c r="M34" t="n">
         <v>1.15</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>16.41</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43984</v>
+        <v>43985</v>
       </c>
       <c r="H35" t="n">
-        <v>44.55</v>
+        <v>47.15</v>
       </c>
       <c r="I35" t="n">
         <v>46.84491822145129</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K35" t="n">
-        <v>57.57</v>
+        <v>55.1</v>
       </c>
       <c r="L35" t="n">
         <v>6.33</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>113</v>
+        <v>114</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>7</v>
+      </c>
+      <c r="U35" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>13.71</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44082</v>
+        <v>44083</v>
       </c>
       <c r="H36" t="n">
-        <v>58.5</v>
+        <v>57.05</v>
       </c>
       <c r="I36" t="n">
         <v>57.97263266942717</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K36" t="n">
-        <v>24.07</v>
+        <v>21</v>
       </c>
       <c r="L36" t="n">
         <v>4.35</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>12.2</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44144</v>
+        <v>44145</v>
       </c>
       <c r="H37" t="n">
-        <v>58.3</v>
+        <v>60.85</v>
       </c>
       <c r="I37" t="n">
         <v>59.72467477584294</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K37" t="n">
-        <v>-2.19</v>
+        <v>-6.66</v>
       </c>
       <c r="L37" t="n">
         <v>7.89</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>11.28</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44271</v>
+        <v>44272</v>
       </c>
       <c r="H38" t="n">
-        <v>118.95</v>
+        <v>111.05</v>
       </c>
       <c r="I38" t="n">
         <v>118.6997687114109</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K38" t="n">
-        <v>95.48</v>
+        <v>82.5</v>
       </c>
       <c r="L38" t="n">
         <v>6.66</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>5</v>
+      </c>
+      <c r="U38" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>21.34</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44326</v>
+        <v>44327</v>
       </c>
       <c r="H39" t="n">
-        <v>112.7</v>
+        <v>118.2</v>
       </c>
       <c r="I39" t="n">
         <v>113.2020321409784</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K39" t="n">
-        <v>-1.49</v>
+        <v>-6.44</v>
       </c>
       <c r="L39" t="n">
         <v>8.640000000000001</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>17.43</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44417</v>
+        <v>44418</v>
       </c>
       <c r="H40" t="n">
-        <v>128.5</v>
+        <v>124.05</v>
       </c>
       <c r="I40" t="n">
         <v>126.0611972278691</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K40" t="n">
-        <v>8.710000000000001</v>
+        <v>4.95</v>
       </c>
       <c r="L40" t="n">
         <v>6.85</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>11.34</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44453</v>
+        <v>44454</v>
       </c>
       <c r="H41" t="n">
-        <v>122.8</v>
+        <v>127.8</v>
       </c>
       <c r="I41" t="n">
         <v>125.4082767717334</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K41" t="n">
-        <v>1.01</v>
+        <v>-3.02</v>
       </c>
       <c r="L41" t="n">
         <v>4.11</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>11.55</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44517</v>
+        <v>44518</v>
       </c>
       <c r="H42" t="n">
-        <v>155.45</v>
+        <v>152.95</v>
       </c>
       <c r="I42" t="n">
         <v>153.563299633993</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K42" t="n">
-        <v>21.64</v>
+        <v>19.68</v>
       </c>
       <c r="L42" t="n">
         <v>7.36</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>15.81</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44588</v>
+        <v>44589</v>
       </c>
       <c r="H43" t="n">
-        <v>139.25</v>
+        <v>143.3</v>
       </c>
       <c r="I43" t="n">
         <v>141.3583714347799</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K43" t="n">
-        <v>8.960000000000001</v>
+        <v>6.31</v>
       </c>
       <c r="L43" t="n">
         <v>3.56</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>4</v>
+      </c>
+      <c r="U43" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -2928,25 +3455,25 @@
         <v>12.13</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44613</v>
+        <v>44614</v>
       </c>
       <c r="H44" t="n">
-        <v>140.5</v>
+        <v>138.85</v>
       </c>
       <c r="I44" t="n">
         <v>139.1181829763291</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K44" t="n">
-        <v>-1.95</v>
+        <v>-3.11</v>
       </c>
       <c r="L44" t="n">
-        <v>3.52</v>
+        <v>5.27</v>
       </c>
       <c r="M44" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="N44" t="n">
         <v>5.63</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>13.51</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44636</v>
+        <v>44637</v>
       </c>
       <c r="H45" t="n">
-        <v>144.4</v>
+        <v>149.45</v>
       </c>
       <c r="I45" t="n">
         <v>148.5746845666827</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K45" t="n">
-        <v>-4</v>
+        <v>-7.63</v>
       </c>
       <c r="L45" t="n">
-        <v>5.87</v>
+        <v>7.96</v>
       </c>
       <c r="M45" t="n">
         <v>8.970000000000001</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>13.62</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44685</v>
+        <v>44686</v>
       </c>
       <c r="H46" t="n">
-        <v>148.1</v>
+        <v>144.15</v>
       </c>
       <c r="I46" t="n">
         <v>147.8731894245352</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.9</v>
+        <v>-3.55</v>
       </c>
       <c r="L46" t="n">
         <v>6.89</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>14.16</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44706</v>
+        <v>44707</v>
       </c>
       <c r="H47" t="n">
-        <v>152.3</v>
+        <v>153</v>
       </c>
       <c r="I47" t="n">
         <v>152.6737286270997</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K47" t="n">
-        <v>-5.65</v>
+        <v>-6.14</v>
       </c>
       <c r="L47" t="n">
         <v>7.77</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>12.99</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44727</v>
+        <v>44728</v>
       </c>
       <c r="H48" t="n">
-        <v>146.05</v>
+        <v>144.2</v>
       </c>
       <c r="I48" t="n">
         <v>144.3648902738096</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K48" t="n">
-        <v>-4.54</v>
+        <v>-5.75</v>
       </c>
       <c r="L48" t="n">
-        <v>6.34</v>
+        <v>6.5</v>
       </c>
       <c r="M48" t="n">
         <v>3.77</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>12.13</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44750</v>
+        <v>44753</v>
       </c>
       <c r="H49" t="n">
-        <v>153.05</v>
+        <v>160.55</v>
       </c>
       <c r="I49" t="n">
         <v>153.6228800668095</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K49" t="n">
-        <v>-6.14</v>
+        <v>-11.34</v>
       </c>
       <c r="L49" t="n">
-        <v>7.25</v>
+        <v>11.65</v>
       </c>
       <c r="M49" t="n">
         <v>0.96</v>
       </c>
       <c r="N49" t="n">
-        <v>3.74</v>
+        <v>4.9</v>
       </c>
       <c r="O49" t="n">
         <v>-1.27</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>12.2</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44827</v>
+        <v>44830</v>
       </c>
       <c r="H50" t="n">
-        <v>188.25</v>
+        <v>177.75</v>
       </c>
       <c r="I50" t="n">
         <v>178.7449744076638</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K50" t="n">
-        <v>17.25</v>
+        <v>10.71</v>
       </c>
       <c r="L50" t="n">
         <v>5.7</v>
@@ -3291,7 +3890,7 @@
         <v>6.52</v>
       </c>
       <c r="N50" t="n">
-        <v>4.4</v>
+        <v>5.58</v>
       </c>
       <c r="O50" t="n">
         <v>4.9</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>13.68</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44851</v>
+        <v>44852</v>
       </c>
       <c r="H51" t="n">
-        <v>195.2</v>
+        <v>205.8</v>
       </c>
       <c r="I51" t="n">
         <v>198.3485490316654</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K51" t="n">
-        <v>-9.82</v>
+        <v>-15.78</v>
       </c>
       <c r="L51" t="n">
-        <v>10.63</v>
+        <v>17.02</v>
       </c>
       <c r="M51" t="n">
         <v>1.88</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>13.97</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44981</v>
+        <v>44984</v>
       </c>
       <c r="H52" t="n">
-        <v>260.2</v>
+        <v>248</v>
       </c>
       <c r="I52" t="n">
         <v>253.6365069096188</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K52" t="n">
-        <v>26.43</v>
+        <v>20.51</v>
       </c>
       <c r="L52" t="n">
         <v>5.59</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>6</v>
+      </c>
+      <c r="U52" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>14.01</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44987</v>
+        <v>44988</v>
       </c>
       <c r="H53" t="n">
-        <v>262.05</v>
+        <v>278.95</v>
       </c>
       <c r="I53" t="n">
         <v>276.4885729018131</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K53" t="n">
-        <v>-5.67</v>
+        <v>-12.48</v>
       </c>
       <c r="L53" t="n">
-        <v>6.55</v>
+        <v>13</v>
       </c>
       <c r="M53" t="n">
-        <v>0.31</v>
+        <v>0.55</v>
       </c>
       <c r="N53" t="n">
-        <v>3.65</v>
+        <v>6.45</v>
       </c>
       <c r="O53" t="n">
         <v>-4.69</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>14.25</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45054</v>
+        <v>45055</v>
       </c>
       <c r="H54" t="n">
-        <v>301.05</v>
+        <v>283.3</v>
       </c>
       <c r="I54" t="n">
         <v>288.4360986701647</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K54" t="n">
-        <v>7.92</v>
+        <v>1.56</v>
       </c>
       <c r="L54" t="n">
         <v>13.07</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>16.62</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45107</v>
+        <v>45110</v>
       </c>
       <c r="H55" t="n">
-        <v>279.3</v>
+        <v>284.35</v>
       </c>
       <c r="I55" t="n">
         <v>279.850168351945</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K55" t="n">
-        <v>1.41</v>
+        <v>-0.37</v>
       </c>
       <c r="L55" t="n">
         <v>8.51</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>7.02</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45253</v>
+        <v>45254</v>
       </c>
       <c r="H56" t="n">
-        <v>394.05</v>
+        <v>389.7</v>
       </c>
       <c r="I56" t="n">
         <v>390.0660822766837</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K56" t="n">
-        <v>38.58</v>
+        <v>37.05</v>
       </c>
       <c r="L56" t="n">
         <v>1.41</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>5</v>
+      </c>
+      <c r="U56" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>10.32</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="H57" t="n">
-        <v>413.2</v>
+        <v>429.1</v>
       </c>
       <c r="I57" t="n">
         <v>424.1512845465671</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K57" t="n">
-        <v>-6.03</v>
+        <v>-10.11</v>
       </c>
       <c r="L57" t="n">
-        <v>10.41</v>
+        <v>10.69</v>
       </c>
       <c r="M57" t="n">
         <v>2.91</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>12.63</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45364</v>
+        <v>45365</v>
       </c>
       <c r="H58" t="n">
-        <v>478.5</v>
+        <v>469.35</v>
       </c>
       <c r="I58" t="n">
         <v>470.7181865360022</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K58" t="n">
-        <v>11.51</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="L58" t="n">
         <v>13</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>4</v>
+      </c>
+      <c r="U58" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>15.82</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45408</v>
+        <v>45411</v>
       </c>
       <c r="H59" t="n">
-        <v>502.7</v>
+        <v>533.75</v>
       </c>
       <c r="I59" t="n">
         <v>526.1433513287084</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K59" t="n">
-        <v>-7.11</v>
+        <v>-13.72</v>
       </c>
       <c r="L59" t="n">
-        <v>11.88</v>
+        <v>14.32</v>
       </c>
       <c r="M59" t="n">
         <v>1.54</v>
       </c>
       <c r="N59" t="n">
-        <v>4.83</v>
+        <v>6.18</v>
       </c>
       <c r="O59" t="n">
         <v>-1.91</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>12.59</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45527</v>
+        <v>45530</v>
       </c>
       <c r="H60" t="n">
-        <v>523.55</v>
+        <v>522.3</v>
       </c>
       <c r="I60" t="n">
         <v>522.3421086027803</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="K60" t="n">
-        <v>-1.91</v>
+        <v>-2.15</v>
       </c>
       <c r="L60" t="n">
         <v>13.88</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>4</v>
+      </c>
+      <c r="U60" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>10.36</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45590</v>
+        <v>45593</v>
       </c>
       <c r="H61" t="n">
-        <v>475.9</v>
+        <v>526.5</v>
       </c>
       <c r="I61" t="n">
         <v>515.9164135299226</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K61" t="n">
-        <v>8.880000000000001</v>
+        <v>-0.8</v>
       </c>
       <c r="L61" t="n">
         <v>5.29</v>
@@ -3918,7 +4649,7 @@
         <v>1.48</v>
       </c>
       <c r="N61" t="n">
-        <v>5.37</v>
+        <v>10.63</v>
       </c>
       <c r="O61" t="n">
         <v>-0.24</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>14.91</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45653</v>
+        <v>45656</v>
       </c>
       <c r="H62" t="n">
-        <v>522.4</v>
+        <v>506.9</v>
       </c>
       <c r="I62" t="n">
         <v>511.7462838600198</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.78</v>
+        <v>-3.72</v>
       </c>
       <c r="L62" t="n">
         <v>10.01</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>4</v>
+      </c>
+      <c r="U62" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>13.9</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45674</v>
+        <v>45677</v>
       </c>
       <c r="H63" t="n">
-        <v>500.75</v>
+        <v>508.15</v>
       </c>
       <c r="I63" t="n">
         <v>507.6756931546558</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K63" t="n">
-        <v>1.21</v>
+        <v>-0.25</v>
       </c>
       <c r="L63" t="n">
         <v>6.23</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>10.22</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45728</v>
+        <v>45729</v>
       </c>
       <c r="H64" t="n">
-        <v>471.5</v>
+        <v>468.2</v>
       </c>
       <c r="I64" t="n">
         <v>468.7181168132714</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K64" t="n">
-        <v>-7.21</v>
+        <v>-7.86</v>
       </c>
       <c r="L64" t="n">
-        <v>8.69</v>
+        <v>10.18</v>
       </c>
       <c r="M64" t="n">
         <v>1.13</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>11.51</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45736</v>
+        <v>45737</v>
       </c>
       <c r="H65" t="n">
-        <v>510.1</v>
+        <v>523.15</v>
       </c>
       <c r="I65" t="n">
         <v>522.1038061559949</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K65" t="n">
-        <v>-8.949999999999999</v>
+        <v>-11.74</v>
       </c>
       <c r="L65" t="n">
-        <v>9.460000000000001</v>
+        <v>12.59</v>
       </c>
       <c r="M65" t="n">
         <v>0.65</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>10.8</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="H66" t="n">
-        <v>841.5</v>
+        <v>795.85</v>
       </c>
       <c r="I66" t="n">
         <v>817.2348222392885</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K66" t="n">
-        <v>60.85</v>
+        <v>52.13</v>
       </c>
       <c r="L66" t="n">
         <v>5.5</v>
@@ -4203,7 +4994,7 @@
         <v>2.91</v>
       </c>
       <c r="N66" t="n">
-        <v>3.67</v>
+        <v>5.42</v>
       </c>
       <c r="O66" t="n">
         <v>2.56</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>173</v>
+        <v>174</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>10</v>
+      </c>
+      <c r="U66" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>11.75</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="H67" t="n">
-        <v>792.15</v>
+        <v>819.8</v>
       </c>
       <c r="I67" t="n">
         <v>808.8684978817555</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K67" t="n">
-        <v>0.46</v>
+        <v>-3.01</v>
       </c>
       <c r="L67" t="n">
         <v>6.3</v>
@@ -4260,7 +5063,7 @@
         <v>0.53</v>
       </c>
       <c r="N67" t="n">
-        <v>3.13</v>
+        <v>3.49</v>
       </c>
       <c r="O67" t="n">
         <v>-5.42</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>8.77</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="H68" t="n">
-        <v>919.8</v>
+        <v>880.15</v>
       </c>
       <c r="I68" t="n">
         <v>891.6910853641403</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K68" t="n">
-        <v>12.2</v>
+        <v>7.36</v>
       </c>
       <c r="L68" t="n">
         <v>3.71</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>11.16</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H69" t="n">
-        <v>886.35</v>
+        <v>936.55</v>
       </c>
       <c r="I69" t="n">
         <v>932.6380391497651</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K69" t="n">
-        <v>-0.7</v>
+        <v>-6.41</v>
       </c>
       <c r="L69" t="n">
-        <v>4.24</v>
+        <v>6.72</v>
       </c>
       <c r="M69" t="n">
         <v>3.98</v>
       </c>
       <c r="N69" t="n">
-        <v>5.01</v>
+        <v>5.66</v>
       </c>
       <c r="O69" t="n">
         <v>-4.31</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>13.38</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="H70" t="n">
-        <v>834.1</v>
+        <v>813.05</v>
       </c>
       <c r="I70" t="n">
         <v>833.685333270827</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K70" t="n">
-        <v>-10.94</v>
+        <v>-13.19</v>
       </c>
       <c r="L70" t="n">
         <v>15.03</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>14.47</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="H71" t="n">
-        <v>853.3</v>
+        <v>876.35</v>
       </c>
       <c r="I71" t="n">
         <v>870.0208547992837</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K71" t="n">
-        <v>-4.95</v>
+        <v>-7.79</v>
       </c>
       <c r="L71" t="n">
-        <v>6.72</v>
+        <v>8.02</v>
       </c>
       <c r="M71" t="n">
         <v>1.91</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,22 +5387,22 @@
         <v>9.15</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="H72" t="n">
-        <v>815.1</v>
+        <v>798.95</v>
       </c>
       <c r="I72" t="n">
         <v>812.7680435160294</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K72" t="n">
-        <v>-6.99</v>
+        <v>-8.83</v>
       </c>
       <c r="L72" t="n">
-        <v>8.6</v>
+        <v>9.91</v>
       </c>
       <c r="M72" t="n">
         <v>0.07000000000000001</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,28 +5456,28 @@
         <v>9.01</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="H73" t="n">
-        <v>793.15</v>
+        <v>870.7</v>
       </c>
       <c r="I73" t="n">
         <v>847.0256975826851</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K73" t="n">
-        <v>0.73</v>
+        <v>-8.98</v>
       </c>
       <c r="L73" t="n">
-        <v>2.7</v>
+        <v>9.51</v>
       </c>
       <c r="M73" t="n">
-        <v>0.36</v>
+        <v>0.86</v>
       </c>
       <c r="N73" t="n">
-        <v>2.69</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="O73" t="n">
         <v>-1.98</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S73" t="b">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>1</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>13.75</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="H74" t="n">
-        <v>853.5</v>
+        <v>836.75</v>
       </c>
       <c r="I74" t="n">
         <v>837.5888216089946</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K74" t="n">
-        <v>-1.98</v>
+        <v>-3.9</v>
       </c>
       <c r="L74" t="n">
         <v>8.720000000000001</v>
@@ -4668,7 +5555,19 @@
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>3</v>
+      </c>
+      <c r="U74" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -4695,22 +5594,22 @@
         <v>8.44</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="H75" t="n">
-        <v>854.1</v>
+        <v>856.85</v>
       </c>
       <c r="I75" t="n">
         <v>854.1931139323941</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K75" t="n">
-        <v>-2.07</v>
+        <v>-2.4</v>
       </c>
       <c r="L75" t="n">
-        <v>3.57</v>
+        <v>4.53</v>
       </c>
       <c r="M75" t="n">
         <v>1.08</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4776,6 +5687,14 @@
       <c r="Q76" t="n">
         <v>7</v>
       </c>
+      <c r="R76" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9734,7 +10653,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>56.4</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6">
@@ -9744,7 +10663,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
@@ -9754,7 +10673,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="8">
@@ -9764,7 +10683,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -9774,7 +10693,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10">
@@ -9784,7 +10703,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>112.1</v>
+        <v>114.5</v>
       </c>
     </row>
     <row r="11">
@@ -9794,7 +10713,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12">
@@ -9804,7 +10723,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13">
@@ -9814,7 +10733,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>35.1</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="14">
@@ -9824,7 +10743,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6.66</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="15">
@@ -9834,7 +10753,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10.2</v>
+        <v>6.17</v>
       </c>
     </row>
     <row r="16">
@@ -9844,7 +10763,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.12</v>
+        <v>-1.72</v>
       </c>
     </row>
     <row r="17">
@@ -9854,7 +10773,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>125.55</v>
+        <v>117.75</v>
       </c>
     </row>
     <row r="18">
@@ -9864,7 +10783,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>48.6</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="19">
@@ -9874,7 +10793,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.98</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="20">
@@ -9884,7 +10803,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7.13</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="21">
@@ -9894,7 +10813,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>21.25</v>
+        <v>23.71</v>
       </c>
     </row>
     <row r="22">
@@ -9904,7 +10823,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23">
@@ -9914,7 +10833,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24">
@@ -9924,7 +10843,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="25">
@@ -9944,7 +10863,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>6.21</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="27">
@@ -9954,7 +10873,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>16.16</v>
+        <v>21.09</v>
       </c>
     </row>
     <row r="28">
@@ -9964,7 +10883,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29">
